--- a/artfynd/A 37063-2025 artfynd.xlsx
+++ b/artfynd/A 37063-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7002178</v>
+        <v>7002177</v>
       </c>
       <c r="B2" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>416040.5973764672</v>
+        <v>416046</v>
       </c>
       <c r="R2" t="n">
-        <v>6971160.126516238</v>
+        <v>6971161</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2013-09-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-09-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7002177</v>
+        <v>7002178</v>
       </c>
       <c r="B3" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416045.6485838837</v>
+        <v>416041</v>
       </c>
       <c r="R3" t="n">
-        <v>6971160.910514724</v>
+        <v>6971160</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2013-09-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-09-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,12 +880,7 @@
         <v>91993034</v>
       </c>
       <c r="B4" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416209.0111450847</v>
+        <v>416209</v>
       </c>
       <c r="R4" t="n">
-        <v>6971038.888430838</v>
+        <v>6971039</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2018-06-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 37063-2025 artfynd.xlsx
+++ b/artfynd/A 37063-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7002177</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7002178</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,8 +990,18 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91993034</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 37063-2025 artfynd.xlsx
+++ b/artfynd/A 37063-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91993034</v>
+        <v>135784703</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,37 +903,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jämtlands län, Hjd</t>
+          <t>Lövdalen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416209</v>
+        <v>416174</v>
       </c>
       <c r="R4" t="n">
-        <v>6971039</v>
+        <v>6971299</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-06-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-10-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,22 +977,1047 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784703</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135784700</v>
+      </c>
+      <c r="B5" t="n">
+        <v>81423</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>416186</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6971268</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784700</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135784702</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92227</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>416174</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6971299</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784702</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135784705</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>416069</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6971115</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784705</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135784697</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>416184</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6971269</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784697</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>91993034</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Jämtlands län, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>416209</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6971039</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-06-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-10-31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Via Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/91993034</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135784699</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>416185</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6971272</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784699</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135784696</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>416195</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6971253</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784696</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135784701</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98142</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>416183</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6971274</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784701</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135784704</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>416209</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6971312</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784704</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135784698</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>416185</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6971268</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784698</t>
         </is>
       </c>
     </row>
@@ -1001,6 +2026,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37063-2025 artfynd.xlsx
+++ b/artfynd/A 37063-2025 artfynd.xlsx
@@ -1099,7 +1099,7 @@
         <v>135784702</v>
       </c>
       <c r="B6" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>135784705</v>
       </c>
       <c r="B7" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>135784701</v>
       </c>
       <c r="B12" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37063-2025 artfynd.xlsx
+++ b/artfynd/A 37063-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>135784703</v>
       </c>
       <c r="B4" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>135784700</v>
       </c>
       <c r="B5" t="n">
-        <v>81423</v>
+        <v>81425</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>135784702</v>
       </c>
       <c r="B6" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>135784705</v>
       </c>
       <c r="B7" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>135784697</v>
       </c>
       <c r="B8" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>135784699</v>
       </c>
       <c r="B10" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135784696</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>135784701</v>
       </c>
       <c r="B12" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>135784704</v>
       </c>
       <c r="B13" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>135784698</v>
       </c>
       <c r="B14" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37063-2025 artfynd.xlsx
+++ b/artfynd/A 37063-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>135784703</v>
       </c>
       <c r="B4" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>135784700</v>
       </c>
       <c r="B5" t="n">
-        <v>81425</v>
+        <v>81426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>135784702</v>
       </c>
       <c r="B6" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>135784705</v>
       </c>
       <c r="B7" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>135784697</v>
       </c>
       <c r="B8" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>135784699</v>
       </c>
       <c r="B10" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>135784701</v>
       </c>
       <c r="B12" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>135784704</v>
       </c>
       <c r="B13" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>135784698</v>
       </c>
       <c r="B14" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37063-2025 artfynd.xlsx
+++ b/artfynd/A 37063-2025 artfynd.xlsx
@@ -1099,7 +1099,7 @@
         <v>135784702</v>
       </c>
       <c r="B6" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>135784705</v>
       </c>
       <c r="B7" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>135784701</v>
       </c>
       <c r="B12" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 37063-2025 artfynd.xlsx
+++ b/artfynd/A 37063-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>135784703</v>
       </c>
       <c r="B4" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>135784700</v>
       </c>
       <c r="B5" t="n">
-        <v>81426</v>
+        <v>81427</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>135784702</v>
       </c>
       <c r="B6" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>135784705</v>
       </c>
       <c r="B7" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>135784697</v>
       </c>
       <c r="B8" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>135784699</v>
       </c>
       <c r="B10" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135784696</v>
       </c>
       <c r="B11" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>135784701</v>
       </c>
       <c r="B12" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>135784704</v>
       </c>
       <c r="B13" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>135784698</v>
       </c>
       <c r="B14" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37063-2025 artfynd.xlsx
+++ b/artfynd/A 37063-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>135784703</v>
       </c>
       <c r="B4" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>135784700</v>
       </c>
       <c r="B5" t="n">
-        <v>81427</v>
+        <v>81431</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>135784702</v>
       </c>
       <c r="B6" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>135784705</v>
       </c>
       <c r="B7" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>135784697</v>
       </c>
       <c r="B8" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>135784699</v>
       </c>
       <c r="B10" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135784696</v>
       </c>
       <c r="B11" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>135784701</v>
       </c>
       <c r="B12" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>135784704</v>
       </c>
       <c r="B13" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>135784698</v>
       </c>
       <c r="B14" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37063-2025 artfynd.xlsx
+++ b/artfynd/A 37063-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>135784703</v>
       </c>
       <c r="B4" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>135784700</v>
       </c>
       <c r="B5" t="n">
-        <v>81431</v>
+        <v>81432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>135784702</v>
       </c>
       <c r="B6" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>135784705</v>
       </c>
       <c r="B7" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>135784697</v>
       </c>
       <c r="B8" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>135784699</v>
       </c>
       <c r="B10" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135784696</v>
       </c>
       <c r="B11" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>135784701</v>
       </c>
       <c r="B12" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>135784704</v>
       </c>
       <c r="B13" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>135784698</v>
       </c>
       <c r="B14" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37063-2025 artfynd.xlsx
+++ b/artfynd/A 37063-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>135784703</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>135784700</v>
       </c>
       <c r="B5" t="n">
-        <v>81432</v>
+        <v>81436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>135784702</v>
       </c>
       <c r="B6" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>135784705</v>
       </c>
       <c r="B7" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>135784697</v>
       </c>
       <c r="B8" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>135784699</v>
       </c>
       <c r="B10" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>135784701</v>
       </c>
       <c r="B12" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>135784704</v>
       </c>
       <c r="B13" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>135784698</v>
       </c>
       <c r="B14" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37063-2025 artfynd.xlsx
+++ b/artfynd/A 37063-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>135784703</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>135784700</v>
       </c>
       <c r="B5" t="n">
-        <v>81436</v>
+        <v>81442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>135784702</v>
       </c>
       <c r="B6" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>135784705</v>
       </c>
       <c r="B7" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>135784697</v>
       </c>
       <c r="B8" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>135784699</v>
       </c>
       <c r="B10" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135784696</v>
       </c>
       <c r="B11" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>135784701</v>
       </c>
       <c r="B12" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>135784704</v>
       </c>
       <c r="B13" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>135784698</v>
       </c>
       <c r="B14" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37063-2025 artfynd.xlsx
+++ b/artfynd/A 37063-2025 artfynd.xlsx
@@ -1099,7 +1099,7 @@
         <v>135784702</v>
       </c>
       <c r="B6" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>135784705</v>
       </c>
       <c r="B7" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>135784701</v>
       </c>
       <c r="B12" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
